--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126125633</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>126125649</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126125710</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>126125669</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>126125633</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>126125649</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126125710</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>126125669</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,6 +1092,932 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126348541</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>421342</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6962830</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126348540</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>421420</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6962900</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126348537</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>421606</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6962786</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126348536</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>421629</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6962773</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126348538</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>421606</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6962795</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126348511</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>421432</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6962635</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Sannolikt tidigare tretå-bohål, ca 1,6m upp i bruten gran</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126348533</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>421761</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6962549</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126348534</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>421772</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6962583</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126348535</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>421837</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6962687</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126125633</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>126125649</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126125710</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>126125669</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>126348541</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>126348540</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126348537</v>
+        <v>126348536</v>
       </c>
       <c r="B8" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1334,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>421606</v>
+        <v>421629</v>
       </c>
       <c r="R8" t="n">
-        <v>6962786</v>
+        <v>6962773</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348536</v>
+        <v>126348537</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421629</v>
+        <v>421606</v>
       </c>
       <c r="R9" t="n">
-        <v>6962773</v>
+        <v>6962786</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,7 +1506,7 @@
         <v>126348538</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>126348511</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>126348533</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>126348534</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>126348535</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -1299,7 +1299,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126348536</v>
+        <v>126348537</v>
       </c>
       <c r="B8" t="n">
         <v>57657</v>
@@ -1334,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>421629</v>
+        <v>421606</v>
       </c>
       <c r="R8" t="n">
-        <v>6962773</v>
+        <v>6962786</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,7 +1401,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348537</v>
+        <v>126348536</v>
       </c>
       <c r="B9" t="n">
         <v>57657</v>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421606</v>
+        <v>421629</v>
       </c>
       <c r="R9" t="n">
-        <v>6962786</v>
+        <v>6962773</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>126125633</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>126125649</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126125710</v>
+        <v>126125669</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421509</v>
+        <v>421399</v>
       </c>
       <c r="R4" t="n">
-        <v>6962716</v>
+        <v>6962782</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126125669</v>
+        <v>126125710</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421399</v>
+        <v>421509</v>
       </c>
       <c r="R5" t="n">
-        <v>6962782</v>
+        <v>6962716</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126348541</v>
+        <v>126348511</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,16 +1124,24 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>421342</v>
+        <v>421432</v>
       </c>
       <c r="R6" t="n">
-        <v>6962830</v>
+        <v>6962635</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Sannolikt tidigare tretå-bohål, ca 1,6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126348540</v>
+        <v>126348533</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1232,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421420</v>
+        <v>421761</v>
       </c>
       <c r="R7" t="n">
-        <v>6962900</v>
+        <v>6962549</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1299,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126348537</v>
+        <v>126348534</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1334,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>421606</v>
+        <v>421772</v>
       </c>
       <c r="R8" t="n">
-        <v>6962786</v>
+        <v>6962583</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348536</v>
+        <v>126348535</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1436,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421629</v>
+        <v>421837</v>
       </c>
       <c r="R9" t="n">
-        <v>6962773</v>
+        <v>6962687</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126348538</v>
+        <v>126348536</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1538,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421606</v>
+        <v>421629</v>
       </c>
       <c r="R10" t="n">
-        <v>6962795</v>
+        <v>6962773</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1605,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126348511</v>
+        <v>126348537</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,24 +1642,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>421432</v>
+        <v>421606</v>
       </c>
       <c r="R11" t="n">
-        <v>6962635</v>
+        <v>6962786</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Sannolikt tidigare tretå-bohål, ca 1,6m upp i bruten gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126348533</v>
+        <v>126348538</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>421761</v>
+        <v>421606</v>
       </c>
       <c r="R12" t="n">
-        <v>6962549</v>
+        <v>6962795</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126348534</v>
+        <v>126348540</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>421772</v>
+        <v>421420</v>
       </c>
       <c r="R13" t="n">
-        <v>6962583</v>
+        <v>6962900</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126348535</v>
+        <v>126348541</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421837</v>
+        <v>421342</v>
       </c>
       <c r="R14" t="n">
-        <v>6962687</v>
+        <v>6962830</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2018,6 +2018,209 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126348542</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>421390</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6962623</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126133773</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>421831</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6962414</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25853-2025 artfynd.xlsx
+++ b/artfynd/A 25853-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126125633</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126125649</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126125669</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126125710</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348511</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348533</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1406,6 +1441,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348534</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348535</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348536</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348537</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1814,6 +1869,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348538</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1916,6 +1976,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348540</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2018,6 +2083,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348541</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2120,6 +2190,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348542</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2221,8 +2296,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126133773</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>